--- a/CP_2569_บันทึกผลจริง_template.xlsx
+++ b/CP_2569_บันทึกผลจริง_template.xlsx
@@ -593,24 +593,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -642,7 +646,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -650,7 +654,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -674,7 +678,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -953,63 +957,63 @@
   <dimension ref="B2:B13"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="115"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="115"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2"/>
+      <c r="B12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1032,1289 +1036,1319 @@
   <dimension ref="A1:AK24"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="23" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="7" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="23" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="U4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="V4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="Z4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AA4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AB4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AC4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AD4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AE4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AF4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AG4" s="5" t="s">
+      <c r="AG4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AH4" s="5" t="s">
+      <c r="AH4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AI4" s="5" t="s">
+      <c r="AI4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AJ4" s="5" t="s">
+      <c r="AJ4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AK4" s="5" t="s">
+      <c r="AK4" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AF5" s="7"/>
-      <c r="AG5" s="7"/>
-      <c r="AH5" s="7"/>
-      <c r="AI5" s="7"/>
-      <c r="AJ5" s="7"/>
-      <c r="AK5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="8"/>
+      <c r="AB5" s="8"/>
+      <c r="AC5" s="8"/>
+      <c r="AD5" s="8"/>
+      <c r="AE5" s="8"/>
+      <c r="AF5" s="8"/>
+      <c r="AG5" s="8"/>
+      <c r="AH5" s="8"/>
+      <c r="AI5" s="8"/>
+      <c r="AJ5" s="8"/>
+      <c r="AK5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="9"/>
-      <c r="AG6" s="9"/>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
-      <c r="AJ6" s="9"/>
-      <c r="AK6" s="9"/>
+      <c r="M6" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="10"/>
+      <c r="AB6" s="10"/>
+      <c r="AC6" s="10"/>
+      <c r="AD6" s="10"/>
+      <c r="AE6" s="10"/>
+      <c r="AF6" s="10"/>
+      <c r="AG6" s="10"/>
+      <c r="AH6" s="10"/>
+      <c r="AI6" s="10"/>
+      <c r="AJ6" s="10"/>
+      <c r="AK6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="9"/>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
-      <c r="AI7" s="9"/>
-      <c r="AJ7" s="9"/>
-      <c r="AK7" s="9"/>
+      <c r="M7" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="10"/>
+      <c r="AK7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="9"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
-      <c r="AF8" s="9"/>
-      <c r="AG8" s="9"/>
-      <c r="AH8" s="9"/>
-      <c r="AI8" s="9"/>
-      <c r="AJ8" s="9"/>
-      <c r="AK8" s="9"/>
+      <c r="M8" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10"/>
+      <c r="AB8" s="10"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="10"/>
+      <c r="AG8" s="10"/>
+      <c r="AH8" s="10"/>
+      <c r="AI8" s="10"/>
+      <c r="AJ8" s="10"/>
+      <c r="AK8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
-      <c r="AE9" s="7"/>
-      <c r="AF9" s="7"/>
-      <c r="AG9" s="7"/>
-      <c r="AH9" s="7"/>
-      <c r="AI9" s="7"/>
-      <c r="AJ9" s="7"/>
-      <c r="AK9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8"/>
+      <c r="AE9" s="8"/>
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="8"/>
+      <c r="AH9" s="8"/>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="K10" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L10" s="11" t="n">
+      <c r="L10" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="9"/>
-      <c r="AC10" s="9"/>
-      <c r="AD10" s="9"/>
-      <c r="AE10" s="9"/>
-      <c r="AF10" s="9"/>
-      <c r="AG10" s="9"/>
-      <c r="AH10" s="9"/>
-      <c r="AI10" s="9"/>
-      <c r="AJ10" s="9"/>
-      <c r="AK10" s="9"/>
+      <c r="M10" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+      <c r="AH10" s="10"/>
+      <c r="AI10" s="10"/>
+      <c r="AJ10" s="10"/>
+      <c r="AK10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="9"/>
-      <c r="AG11" s="9"/>
-      <c r="AH11" s="9"/>
-      <c r="AI11" s="9"/>
-      <c r="AJ11" s="9"/>
-      <c r="AK11" s="9"/>
+      <c r="M11" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="10"/>
+      <c r="AF11" s="10"/>
+      <c r="AG11" s="10"/>
+      <c r="AH11" s="10"/>
+      <c r="AI11" s="10"/>
+      <c r="AJ11" s="10"/>
+      <c r="AK11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="9"/>
-      <c r="AG12" s="9"/>
-      <c r="AH12" s="9"/>
-      <c r="AI12" s="9"/>
-      <c r="AJ12" s="9"/>
-      <c r="AK12" s="9"/>
+      <c r="M12" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
+      <c r="AF12" s="10"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="10"/>
+      <c r="AK12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
-      <c r="AE13" s="7"/>
-      <c r="AF13" s="7"/>
-      <c r="AG13" s="7"/>
-      <c r="AH13" s="7"/>
-      <c r="AI13" s="7"/>
-      <c r="AJ13" s="7"/>
-      <c r="AK13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="8"/>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="I14" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J14" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="9"/>
-      <c r="AC14" s="9"/>
-      <c r="AD14" s="9"/>
-      <c r="AE14" s="9"/>
-      <c r="AF14" s="9"/>
-      <c r="AG14" s="9"/>
-      <c r="AH14" s="9"/>
-      <c r="AI14" s="9"/>
-      <c r="AJ14" s="9"/>
-      <c r="AK14" s="9"/>
+      <c r="M14" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="10"/>
+      <c r="AG14" s="10"/>
+      <c r="AH14" s="10"/>
+      <c r="AI14" s="10"/>
+      <c r="AJ14" s="10"/>
+      <c r="AK14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="I15" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="9"/>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="9"/>
-      <c r="AG15" s="9"/>
-      <c r="AH15" s="9"/>
-      <c r="AI15" s="9"/>
-      <c r="AJ15" s="9"/>
-      <c r="AK15" s="9"/>
+      <c r="M15" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+      <c r="AD15" s="10"/>
+      <c r="AE15" s="10"/>
+      <c r="AF15" s="10"/>
+      <c r="AG15" s="10"/>
+      <c r="AH15" s="10"/>
+      <c r="AI15" s="10"/>
+      <c r="AJ15" s="10"/>
+      <c r="AK15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="9"/>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="9"/>
-      <c r="AF16" s="9"/>
-      <c r="AG16" s="9"/>
-      <c r="AH16" s="9"/>
-      <c r="AI16" s="9"/>
-      <c r="AJ16" s="9"/>
-      <c r="AK16" s="9"/>
+      <c r="M16" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
+      <c r="AI16" s="10"/>
+      <c r="AJ16" s="10"/>
+      <c r="AK16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
-      <c r="AE17" s="7"/>
-      <c r="AF17" s="7"/>
-      <c r="AG17" s="7"/>
-      <c r="AH17" s="7"/>
-      <c r="AI17" s="7"/>
-      <c r="AJ17" s="7"/>
-      <c r="AK17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="11" t="n">
+      <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
-      <c r="AC18" s="9"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
-      <c r="AF18" s="9"/>
-      <c r="AG18" s="9"/>
-      <c r="AH18" s="9"/>
-      <c r="AI18" s="9"/>
-      <c r="AJ18" s="9"/>
-      <c r="AK18" s="9"/>
+      <c r="M18" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
+      <c r="AF18" s="10"/>
+      <c r="AG18" s="10"/>
+      <c r="AH18" s="10"/>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="11" t="n">
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="9"/>
-      <c r="AG19" s="9"/>
-      <c r="AH19" s="9"/>
-      <c r="AI19" s="9"/>
-      <c r="AJ19" s="9"/>
-      <c r="AK19" s="9"/>
+      <c r="M19" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+      <c r="AD19" s="10"/>
+      <c r="AE19" s="10"/>
+      <c r="AF19" s="10"/>
+      <c r="AG19" s="10"/>
+      <c r="AH19" s="10"/>
+      <c r="AI19" s="10"/>
+      <c r="AJ19" s="10"/>
+      <c r="AK19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="11" t="n">
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="9"/>
-      <c r="AG20" s="9"/>
-      <c r="AH20" s="9"/>
-      <c r="AI20" s="9"/>
-      <c r="AJ20" s="9"/>
-      <c r="AK20" s="9"/>
+      <c r="M20" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="10"/>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="10"/>
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="10"/>
+      <c r="AJ20" s="10"/>
+      <c r="AK20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-      <c r="X21" s="9"/>
-      <c r="Y21" s="9"/>
-      <c r="Z21" s="9"/>
-      <c r="AA21" s="9"/>
-      <c r="AB21" s="9"/>
-      <c r="AC21" s="9"/>
-      <c r="AD21" s="9"/>
-      <c r="AE21" s="9"/>
-      <c r="AF21" s="9"/>
-      <c r="AG21" s="9"/>
-      <c r="AH21" s="9"/>
-      <c r="AI21" s="9"/>
-      <c r="AJ21" s="9"/>
-      <c r="AK21" s="9"/>
+      <c r="G21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+      <c r="AD21" s="10"/>
+      <c r="AE21" s="10"/>
+      <c r="AF21" s="10"/>
+      <c r="AG21" s="10"/>
+      <c r="AH21" s="10"/>
+      <c r="AI21" s="10"/>
+      <c r="AJ21" s="10"/>
+      <c r="AK21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7"/>
-      <c r="AD22" s="7"/>
-      <c r="AE22" s="7"/>
-      <c r="AF22" s="7"/>
-      <c r="AG22" s="7"/>
-      <c r="AH22" s="7"/>
-      <c r="AI22" s="7"/>
-      <c r="AJ22" s="7"/>
-      <c r="AK22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8"/>
+      <c r="AD22" s="8"/>
+      <c r="AE22" s="8"/>
+      <c r="AF22" s="8"/>
+      <c r="AG22" s="8"/>
+      <c r="AH22" s="8"/>
+      <c r="AI22" s="8"/>
+      <c r="AJ22" s="8"/>
+      <c r="AK22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="9"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="9"/>
-      <c r="AG23" s="9"/>
-      <c r="AH23" s="9"/>
-      <c r="AI23" s="9"/>
-      <c r="AJ23" s="9"/>
-      <c r="AK23" s="9"/>
+      <c r="G23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10"/>
+      <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10"/>
+      <c r="AF23" s="10"/>
+      <c r="AG23" s="10"/>
+      <c r="AH23" s="10"/>
+      <c r="AI23" s="10"/>
+      <c r="AJ23" s="10"/>
+      <c r="AK23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="9"/>
-      <c r="W24" s="9"/>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="9"/>
-      <c r="Z24" s="9"/>
-      <c r="AA24" s="9"/>
-      <c r="AB24" s="9"/>
-      <c r="AC24" s="9"/>
-      <c r="AD24" s="9"/>
-      <c r="AE24" s="9"/>
-      <c r="AF24" s="9"/>
-      <c r="AG24" s="9"/>
-      <c r="AH24" s="9"/>
-      <c r="AI24" s="9"/>
-      <c r="AJ24" s="9"/>
-      <c r="AK24" s="9"/>
+      <c r="G24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+      <c r="AA24" s="10"/>
+      <c r="AB24" s="10"/>
+      <c r="AC24" s="10"/>
+      <c r="AD24" s="10"/>
+      <c r="AE24" s="10"/>
+      <c r="AF24" s="10"/>
+      <c r="AG24" s="10"/>
+      <c r="AH24" s="10"/>
+      <c r="AI24" s="10"/>
+      <c r="AJ24" s="10"/>
+      <c r="AK24" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2342,1022 +2376,1022 @@
   <dimension ref="A1:N28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="13" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
+      <c r="C1" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="16" t="n">
         <f aca="false">MATCH(C1,บันทึกผล!$G$4:$U$4,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="str">
+    <row r="5" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A6,FIND(".",บันทึกผล!A6)-1)</f>
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="str">
+      <c r="B5" s="18" t="str">
         <f aca="false">บันทึกผล!A6</f>
         <v>1.1</v>
       </c>
-      <c r="C5" s="18" t="str">
+      <c r="C5" s="19" t="str">
         <f aca="false">บันทึกผล!B6</f>
         <v>รวบรวม ศึกษา วิเคราะห์กฎหมาย กฎ ระเบียบที่สำคัญที่เกี่ยวข้องกับการดำเนินงาน</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">บันทึกผล!D6</f>
         <v>34</v>
       </c>
-      <c r="E5" s="17" t="str">
+      <c r="E5" s="18" t="str">
         <f aca="false">บันทึกผล!E6</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F5" s="17" t="str">
+      <c r="F5" s="18" t="str">
         <f aca="false">บันทึกผล!F6</f>
         <v>ม.ค.70</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="20" t="n">
         <f aca="false">N5-M5+1</f>
         <v>13</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="20" t="n">
         <f aca="false">IF($C$2&lt;M5,0,IF($C$2&gt;=N5,100,ROUND(($C$2-M5+1)/(N5-M5+1)*100,0)))</f>
-        <v>46</v>
-      </c>
-      <c r="I5" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="I5" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G6:INDEX(บันทึกผล!$G6:$U6,$C$2)),0)</f>
-        <v>46</v>
-      </c>
-      <c r="J5" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="J5" s="20" t="n">
         <f aca="false">I5-H5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="17" t="str">
+      <c r="K5" s="18" t="str">
         <f aca="false">IF(H5=0,"รอกำหนด",IF(I5&gt;=H5,"ตามแผน",IF(H5-I5&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <f aca="false">MATCH(E5,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <f aca="false">MATCH(F5,บันทึกผล!$G$4:$U$4,0)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="str">
+    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A7,FIND(".",บันทึกผล!A7)-1)</f>
         <v>1</v>
       </c>
-      <c r="B6" s="17" t="str">
+      <c r="B6" s="18" t="str">
         <f aca="false">บันทึกผล!A7</f>
         <v>1.2</v>
       </c>
-      <c r="C6" s="18" t="str">
+      <c r="C6" s="19" t="str">
         <f aca="false">บันทึกผล!B7</f>
         <v>ปรับปรุงทะเบียนกฎหมาย กฎ ระเบียบที่สำคัญที่เกี่ยวข้องกับการดำเนินงาน (Compliance Universe)</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <f aca="false">บันทึกผล!D7</f>
         <v>33</v>
       </c>
-      <c r="E6" s="17" t="str">
+      <c r="E6" s="18" t="str">
         <f aca="false">บันทึกผล!E7</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F6" s="17" t="str">
+      <c r="F6" s="18" t="str">
         <f aca="false">บันทึกผล!F7</f>
         <v>ธ.ค.69</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="20" t="n">
         <f aca="false">N6-M6+1</f>
         <v>12</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="20" t="n">
         <f aca="false">IF($C$2&lt;M6,0,IF($C$2&gt;=N6,100,ROUND(($C$2-M6+1)/(N6-M6+1)*100,0)))</f>
-        <v>50</v>
-      </c>
-      <c r="I6" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="I6" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G7:INDEX(บันทึกผล!$G7:$U7,$C$2)),0)</f>
-        <v>50</v>
-      </c>
-      <c r="J6" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="J6" s="20" t="n">
         <f aca="false">I6-H6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="17" t="str">
+      <c r="K6" s="18" t="str">
         <f aca="false">IF(H6=0,"รอกำหนด",IF(I6&gt;=H6,"ตามแผน",IF(H6-I6&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <f aca="false">MATCH(E6,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <f aca="false">MATCH(F6,บันทึกผล!$G$4:$U$4,0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="str">
+    <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A8,FIND(".",บันทึกผล!A8)-1)</f>
         <v>1</v>
       </c>
-      <c r="B7" s="17" t="str">
+      <c r="B7" s="18" t="str">
         <f aca="false">บันทึกผล!A8</f>
         <v>1.3</v>
       </c>
-      <c r="C7" s="18" t="str">
+      <c r="C7" s="19" t="str">
         <f aca="false">บันทึกผล!B8</f>
         <v>ปรับปรุงระเบียบ ข้อบังคับ คำสั่ง นโยบาย มาตรฐานการปฏิบัติงานให้สอดคล้องกับกฎหมาย กฎ ระเบียบที่เกี่ยวข้องที่ปรับปรุงหรือเป็นเรื่องใหม่</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">บันทึกผล!D8</f>
         <v>33</v>
       </c>
-      <c r="E7" s="17" t="str">
+      <c r="E7" s="18" t="str">
         <f aca="false">บันทึกผล!E8</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F7" s="17" t="str">
+      <c r="F7" s="18" t="str">
         <f aca="false">บันทึกผล!F8</f>
         <v>ธ.ค.69</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="20" t="n">
         <f aca="false">N7-M7+1</f>
         <v>12</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="20" t="n">
         <f aca="false">IF($C$2&lt;M7,0,IF($C$2&gt;=N7,100,ROUND(($C$2-M7+1)/(N7-M7+1)*100,0)))</f>
-        <v>50</v>
-      </c>
-      <c r="I7" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="I7" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G8:INDEX(บันทึกผล!$G8:$U8,$C$2)),0)</f>
-        <v>50</v>
-      </c>
-      <c r="J7" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="J7" s="20" t="n">
         <f aca="false">I7-H7</f>
         <v>0</v>
       </c>
-      <c r="K7" s="17" t="str">
+      <c r="K7" s="18" t="str">
         <f aca="false">IF(H7=0,"รอกำหนด",IF(I7&gt;=H7,"ตามแผน",IF(H7-I7&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <f aca="false">MATCH(E7,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <f aca="false">MATCH(F7,บันทึกผล!$G$4:$U$4,0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="str">
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A10,FIND(".",บันทึกผล!A10)-1)</f>
         <v>2</v>
       </c>
-      <c r="B8" s="17" t="str">
+      <c r="B8" s="18" t="str">
         <f aca="false">บันทึกผล!A10</f>
         <v>2.1</v>
       </c>
-      <c r="C8" s="18" t="str">
+      <c r="C8" s="19" t="str">
         <f aca="false">บันทึกผล!B10</f>
         <v>วิเคราะห์สาเหตุและผลกระทบ และประเมินความเสี่ยงจากการไม่สามารถปฏิบัติตามกฎ ระเบียบ</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <f aca="false">บันทึกผล!D10</f>
         <v>34</v>
       </c>
-      <c r="E8" s="17" t="str">
+      <c r="E8" s="18" t="str">
         <f aca="false">บันทึกผล!E10</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F8" s="17" t="str">
+      <c r="F8" s="18" t="str">
         <f aca="false">บันทึกผล!F10</f>
         <v>ธ.ค.69</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="20" t="n">
         <f aca="false">N8-M8+1</f>
         <v>12</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="20" t="n">
         <f aca="false">IF($C$2&lt;M8,0,IF($C$2&gt;=N8,100,ROUND(($C$2-M8+1)/(N8-M8+1)*100,0)))</f>
-        <v>50</v>
-      </c>
-      <c r="I8" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="I8" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G10:INDEX(บันทึกผล!$G10:$U10,$C$2)),0)</f>
-        <v>50</v>
-      </c>
-      <c r="J8" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="J8" s="20" t="n">
         <f aca="false">I8-H8</f>
         <v>0</v>
       </c>
-      <c r="K8" s="17" t="str">
+      <c r="K8" s="18" t="str">
         <f aca="false">IF(H8=0,"รอกำหนด",IF(I8&gt;=H8,"ตามแผน",IF(H8-I8&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <f aca="false">MATCH(E8,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <f aca="false">MATCH(F8,บันทึกผล!$G$4:$U$4,0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="str">
+    <row r="9" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A11,FIND(".",บันทึกผล!A11)-1)</f>
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="str">
+      <c r="B9" s="18" t="str">
         <f aca="false">บันทึกผล!A11</f>
         <v>2.2</v>
       </c>
-      <c r="C9" s="18" t="str">
+      <c r="C9" s="19" t="str">
         <f aca="false">บันทึกผล!B11</f>
         <v>สรุปรายการ Compliance Risk ที่สำคัญที่ต้องกำหนด/ปรับปรุงการควบคุม</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <f aca="false">บันทึกผล!D11</f>
         <v>33</v>
       </c>
-      <c r="E9" s="17" t="str">
+      <c r="E9" s="18" t="str">
         <f aca="false">บันทึกผล!E11</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F9" s="17" t="str">
+      <c r="F9" s="18" t="str">
         <f aca="false">บันทึกผล!F11</f>
         <v>มิ.ย.69</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="20" t="n">
         <f aca="false">N9-M9+1</f>
         <v>6</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="20" t="n">
         <f aca="false">IF($C$2&lt;M9,0,IF($C$2&gt;=N9,100,ROUND(($C$2-M9+1)/(N9-M9+1)*100,0)))</f>
         <v>100</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G11:INDEX(บันทึกผล!$G11:$U11,$C$2)),0)</f>
         <v>100</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="20" t="n">
         <f aca="false">I9-H9</f>
         <v>0</v>
       </c>
-      <c r="K9" s="17" t="str">
+      <c r="K9" s="18" t="str">
         <f aca="false">IF(H9=0,"รอกำหนด",IF(I9&gt;=H9,"ตามแผน",IF(H9-I9&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <f aca="false">MATCH(E9,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <f aca="false">MATCH(F9,บันทึกผล!$G$4:$U$4,0)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="str">
+    <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A12,FIND(".",บันทึกผล!A12)-1)</f>
         <v>2</v>
       </c>
-      <c r="B10" s="17" t="str">
+      <c r="B10" s="18" t="str">
         <f aca="false">บันทึกผล!A12</f>
         <v>2.3</v>
       </c>
-      <c r="C10" s="18" t="str">
+      <c r="C10" s="19" t="str">
         <f aca="false">บันทึกผล!B12</f>
         <v>จัดวาง/ทบทวนระบบการควบคุมภายในของกระบวนงานพื้นฐานและกระบวนงานตามภารกิจของทุกหน่วยงาน</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <f aca="false">บันทึกผล!D12</f>
         <v>33</v>
       </c>
-      <c r="E10" s="17" t="str">
+      <c r="E10" s="18" t="str">
         <f aca="false">บันทึกผล!E12</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F10" s="17" t="str">
+      <c r="F10" s="18" t="str">
         <f aca="false">บันทึกผล!F12</f>
         <v>ธ.ค.69</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">N10-M10+1</f>
         <v>12</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="20" t="n">
         <f aca="false">IF($C$2&lt;M10,0,IF($C$2&gt;=N10,100,ROUND(($C$2-M10+1)/(N10-M10+1)*100,0)))</f>
-        <v>50</v>
-      </c>
-      <c r="I10" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="I10" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G12:INDEX(บันทึกผล!$G12:$U12,$C$2)),0)</f>
-        <v>50</v>
-      </c>
-      <c r="J10" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="J10" s="20" t="n">
         <f aca="false">I10-H10</f>
         <v>0</v>
       </c>
-      <c r="K10" s="17" t="str">
+      <c r="K10" s="18" t="str">
         <f aca="false">IF(H10=0,"รอกำหนด",IF(I10&gt;=H10,"ตามแผน",IF(H10-I10&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <f aca="false">MATCH(E10,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <f aca="false">MATCH(F10,บันทึกผล!$G$4:$U$4,0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="str">
+    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A14,FIND(".",บันทึกผล!A14)-1)</f>
         <v>3</v>
       </c>
-      <c r="B11" s="17" t="str">
+      <c r="B11" s="18" t="str">
         <f aca="false">บันทึกผล!A14</f>
         <v>3.1</v>
       </c>
-      <c r="C11" s="18" t="str">
+      <c r="C11" s="19" t="str">
         <f aca="false">บันทึกผล!B14</f>
         <v>สื่อสาร อบรม เพื่อสร้างความรู้ความเข้าใจและความตระหนักเกี่ยวกับนโยบาย กรอบและแนวทางการปฏิบัติตามกฎ ระเบียบ</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <f aca="false">บันทึกผล!D14</f>
         <v>34</v>
       </c>
-      <c r="E11" s="17" t="str">
+      <c r="E11" s="18" t="str">
         <f aca="false">บันทึกผล!E14</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F11" s="17" t="str">
+      <c r="F11" s="18" t="str">
         <f aca="false">บันทึกผล!F14</f>
         <v>ม.ค.70</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <f aca="false">N11-M11+1</f>
         <v>13</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="20" t="n">
         <f aca="false">IF($C$2&lt;M11,0,IF($C$2&gt;=N11,100,ROUND(($C$2-M11+1)/(N11-M11+1)*100,0)))</f>
-        <v>46</v>
-      </c>
-      <c r="I11" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="I11" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G14:INDEX(บันทึกผล!$G14:$U14,$C$2)),0)</f>
-        <v>46</v>
-      </c>
-      <c r="J11" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="J11" s="20" t="n">
         <f aca="false">I11-H11</f>
         <v>0</v>
       </c>
-      <c r="K11" s="17" t="str">
+      <c r="K11" s="18" t="str">
         <f aca="false">IF(H11=0,"รอกำหนด",IF(I11&gt;=H11,"ตามแผน",IF(H11-I11&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <f aca="false">MATCH(E11,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <f aca="false">MATCH(F11,บันทึกผล!$G$4:$U$4,0)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="str">
+    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A15,FIND(".",บันทึกผล!A15)-1)</f>
         <v>3</v>
       </c>
-      <c r="B12" s="17" t="str">
+      <c r="B12" s="18" t="str">
         <f aca="false">บันทึกผล!A15</f>
         <v>3.2</v>
       </c>
-      <c r="C12" s="18" t="str">
+      <c r="C12" s="19" t="str">
         <f aca="false">บันทึกผล!B15</f>
         <v>สื่อสาร อบรม เกี่ยวกับกฎหมาย กฎ ระเบียบที่เกี่ยวข้องที่ปรับปรุงหรือเป็นเรื่องใหม่</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <f aca="false">บันทึกผล!D15</f>
         <v>33</v>
       </c>
-      <c r="E12" s="17" t="str">
+      <c r="E12" s="18" t="str">
         <f aca="false">บันทึกผล!E15</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F12" s="17" t="str">
+      <c r="F12" s="18" t="str">
         <f aca="false">บันทึกผล!F15</f>
         <v>ม.ค.70</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <f aca="false">N12-M12+1</f>
         <v>13</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="20" t="n">
         <f aca="false">IF($C$2&lt;M12,0,IF($C$2&gt;=N12,100,ROUND(($C$2-M12+1)/(N12-M12+1)*100,0)))</f>
-        <v>46</v>
-      </c>
-      <c r="I12" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="I12" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G15:INDEX(บันทึกผล!$G15:$U15,$C$2)),0)</f>
-        <v>46</v>
-      </c>
-      <c r="J12" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="J12" s="20" t="n">
         <f aca="false">I12-H12</f>
         <v>0</v>
       </c>
-      <c r="K12" s="17" t="str">
+      <c r="K12" s="18" t="str">
         <f aca="false">IF(H12=0,"รอกำหนด",IF(I12&gt;=H12,"ตามแผน",IF(H12-I12&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <f aca="false">MATCH(E12,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <f aca="false">MATCH(F12,บันทึกผล!$G$4:$U$4,0)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="str">
+    <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A16,FIND(".",บันทึกผล!A16)-1)</f>
         <v>3</v>
       </c>
-      <c r="B13" s="17" t="str">
+      <c r="B13" s="18" t="str">
         <f aca="false">บันทึกผล!A16</f>
         <v>3.3</v>
       </c>
-      <c r="C13" s="18" t="str">
+      <c r="C13" s="19" t="str">
         <f aca="false">บันทึกผล!B16</f>
         <v>ประสานงาน ให้คำปรึกษาแนะนำหน่วยงาน เพื่อทบทวนการดำเนินงานให้สอดคล้องกับกฎหมาย กฎ ระเบียบที่เกี่ยวข้องที่ปรับปรุงหรือเป็นเรื่องใหม่</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <f aca="false">บันทึกผล!D16</f>
         <v>33</v>
       </c>
-      <c r="E13" s="17" t="str">
+      <c r="E13" s="18" t="str">
         <f aca="false">บันทึกผล!E16</f>
         <v>ม.ค.69</v>
       </c>
-      <c r="F13" s="17" t="str">
+      <c r="F13" s="18" t="str">
         <f aca="false">บันทึกผล!F16</f>
         <v>ม.ค.70</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="20" t="n">
         <f aca="false">N13-M13+1</f>
         <v>13</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="20" t="n">
         <f aca="false">IF($C$2&lt;M13,0,IF($C$2&gt;=N13,100,ROUND(($C$2-M13+1)/(N13-M13+1)*100,0)))</f>
-        <v>46</v>
-      </c>
-      <c r="I13" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="I13" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G16:INDEX(บันทึกผล!$G16:$U16,$C$2)),0)</f>
-        <v>46</v>
-      </c>
-      <c r="J13" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="J13" s="20" t="n">
         <f aca="false">I13-H13</f>
         <v>0</v>
       </c>
-      <c r="K13" s="17" t="str">
+      <c r="K13" s="18" t="str">
         <f aca="false">IF(H13=0,"รอกำหนด",IF(I13&gt;=H13,"ตามแผน",IF(H13-I13&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <f aca="false">MATCH(E13,บันทึกผล!$G$4:$U$4,0)</f>
         <v>1</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <f aca="false">MATCH(F13,บันทึกผล!$G$4:$U$4,0)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="str">
+    <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A18,FIND(".",บันทึกผล!A18)-1)</f>
         <v>4</v>
       </c>
-      <c r="B14" s="17" t="str">
+      <c r="B14" s="18" t="str">
         <f aca="false">บันทึกผล!A18</f>
         <v>4.1</v>
       </c>
-      <c r="C14" s="18" t="str">
+      <c r="C14" s="19" t="str">
         <f aca="false">บันทึกผล!B18</f>
         <v>สอบทานการปฏิบัติตามกฎระเบียบด้วยตนเองในทุกกระบวนงานที่ได้จัดวางระบบการควบคุมภายในไว้</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">บันทึกผล!D18</f>
         <v>25</v>
       </c>
-      <c r="E14" s="17" t="str">
+      <c r="E14" s="18" t="str">
         <f aca="false">บันทึกผล!E18</f>
         <v>พ.ค.69</v>
       </c>
-      <c r="F14" s="17" t="str">
+      <c r="F14" s="18" t="str">
         <f aca="false">บันทึกผล!F18</f>
         <v>ต.ค.69</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="20" t="n">
         <f aca="false">N14-M14+1</f>
         <v>6</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="20" t="n">
         <f aca="false">IF($C$2&lt;M14,0,IF($C$2&gt;=N14,100,ROUND(($C$2-M14+1)/(N14-M14+1)*100,0)))</f>
-        <v>33</v>
-      </c>
-      <c r="I14" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G18:INDEX(บันทึกผล!$G18:$U18,$C$2)),0)</f>
-        <v>33</v>
-      </c>
-      <c r="J14" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" s="20" t="n">
         <f aca="false">I14-H14</f>
         <v>0</v>
       </c>
-      <c r="K14" s="17" t="str">
+      <c r="K14" s="18" t="str">
         <f aca="false">IF(H14=0,"รอกำหนด",IF(I14&gt;=H14,"ตามแผน",IF(H14-I14&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="1" t="n">
         <f aca="false">MATCH(E14,บันทึกผล!$G$4:$U$4,0)</f>
         <v>5</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="1" t="n">
         <f aca="false">MATCH(F14,บันทึกผล!$G$4:$U$4,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="str">
+    <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A19,FIND(".",บันทึกผล!A19)-1)</f>
         <v>4</v>
       </c>
-      <c r="B15" s="17" t="str">
+      <c r="B15" s="18" t="str">
         <f aca="false">บันทึกผล!A19</f>
         <v>4.2</v>
       </c>
-      <c r="C15" s="18" t="str">
+      <c r="C15" s="19" t="str">
         <f aca="false">บันทึกผล!B19</f>
         <v>สอบทานการปฏิบัติตามกฎระเบียบในกระบวนการปฏิบัติงานที่มีความเสี่ยงที่อาจทำให้ไม่สามารถปฏิบัติตามกฎ ระเบียบ และสรุปรายงานผลการสอบทานฯ</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <f aca="false">บันทึกผล!D19</f>
         <v>25</v>
       </c>
-      <c r="E15" s="17" t="str">
+      <c r="E15" s="18" t="str">
         <f aca="false">บันทึกผล!E19</f>
         <v>มิ.ย.69</v>
       </c>
-      <c r="F15" s="17" t="str">
+      <c r="F15" s="18" t="str">
         <f aca="false">บันทึกผล!F19</f>
         <v>ธ.ค.69</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="20" t="n">
         <f aca="false">N15-M15+1</f>
         <v>7</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="20" t="n">
         <f aca="false">IF($C$2&lt;M15,0,IF($C$2&gt;=N15,100,ROUND(($C$2-M15+1)/(N15-M15+1)*100,0)))</f>
-        <v>14</v>
-      </c>
-      <c r="I15" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="I15" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G19:INDEX(บันทึกผล!$G19:$U19,$C$2)),0)</f>
-        <v>14</v>
-      </c>
-      <c r="J15" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="J15" s="20" t="n">
         <f aca="false">I15-H15</f>
         <v>0</v>
       </c>
-      <c r="K15" s="17" t="str">
+      <c r="K15" s="18" t="str">
         <f aca="false">IF(H15=0,"รอกำหนด",IF(I15&gt;=H15,"ตามแผน",IF(H15-I15&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="1" t="n">
         <f aca="false">MATCH(E15,บันทึกผล!$G$4:$U$4,0)</f>
         <v>6</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="1" t="n">
         <f aca="false">MATCH(F15,บันทึกผล!$G$4:$U$4,0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="str">
+    <row r="16" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A20,FIND(".",บันทึกผล!A20)-1)</f>
         <v>4</v>
       </c>
-      <c r="B16" s="17" t="str">
+      <c r="B16" s="18" t="str">
         <f aca="false">บันทึกผล!A20</f>
         <v>4.3</v>
       </c>
-      <c r="C16" s="18" t="str">
+      <c r="C16" s="19" t="str">
         <f aca="false">บันทึกผล!B20</f>
         <v>ประเมินการปฏิบัติตามกฎระเบียบด้วยตนเอง (Compliance Self-Assessment)</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <f aca="false">บันทึกผล!D20</f>
         <v>25</v>
       </c>
-      <c r="E16" s="17" t="str">
+      <c r="E16" s="18" t="str">
         <f aca="false">บันทึกผล!E20</f>
         <v>มิ.ย.69</v>
       </c>
-      <c r="F16" s="17" t="str">
+      <c r="F16" s="18" t="str">
         <f aca="false">บันทึกผล!F20</f>
         <v>ธ.ค.69</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="20" t="n">
         <f aca="false">N16-M16+1</f>
         <v>7</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="20" t="n">
         <f aca="false">IF($C$2&lt;M16,0,IF($C$2&gt;=N16,100,ROUND(($C$2-M16+1)/(N16-M16+1)*100,0)))</f>
-        <v>14</v>
-      </c>
-      <c r="I16" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="I16" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G20:INDEX(บันทึกผล!$G20:$U20,$C$2)),0)</f>
-        <v>14</v>
-      </c>
-      <c r="J16" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="J16" s="20" t="n">
         <f aca="false">I16-H16</f>
         <v>0</v>
       </c>
-      <c r="K16" s="17" t="str">
+      <c r="K16" s="18" t="str">
         <f aca="false">IF(H16=0,"รอกำหนด",IF(I16&gt;=H16,"ตามแผน",IF(H16-I16&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="1" t="n">
         <f aca="false">MATCH(E16,บันทึกผล!$G$4:$U$4,0)</f>
         <v>6</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="1" t="n">
         <f aca="false">MATCH(F16,บันทึกผล!$G$4:$U$4,0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="str">
+    <row r="17" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A21,FIND(".",บันทึกผล!A21)-1)</f>
         <v>4</v>
       </c>
-      <c r="B17" s="17" t="str">
+      <c r="B17" s="18" t="str">
         <f aca="false">บันทึกผล!A21</f>
         <v>4.4</v>
       </c>
-      <c r="C17" s="18" t="str">
+      <c r="C17" s="19" t="str">
         <f aca="false">บันทึกผล!B21</f>
         <v>นำผลประเมินมาปรับปรุงการปฏิบัติงานเพื่อให้เป็นไปตามกฎหมาย กฎ ระเบียบ</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">บันทึกผล!D21</f>
         <v>25</v>
       </c>
-      <c r="E17" s="17" t="str">
+      <c r="E17" s="18" t="str">
         <f aca="false">บันทึกผล!E21</f>
         <v>ต.ค.69</v>
       </c>
-      <c r="F17" s="17" t="str">
+      <c r="F17" s="18" t="str">
         <f aca="false">บันทึกผล!F21</f>
         <v>มี.ค.70</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="20" t="n">
         <f aca="false">N17-M17+1</f>
         <v>6</v>
       </c>
-      <c r="H17" s="19" t="n">
+      <c r="H17" s="20" t="n">
         <f aca="false">IF($C$2&lt;M17,0,IF($C$2&gt;=N17,100,ROUND(($C$2-M17+1)/(N17-M17+1)*100,0)))</f>
         <v>0</v>
       </c>
-      <c r="I17" s="19" t="n">
+      <c r="I17" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G21:INDEX(บันทึกผล!$G21:$U21,$C$2)),0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="J17" s="20" t="n">
         <f aca="false">I17-H17</f>
         <v>0</v>
       </c>
-      <c r="K17" s="17" t="str">
+      <c r="K17" s="18" t="str">
         <f aca="false">IF(H17=0,"รอกำหนด",IF(I17&gt;=H17,"ตามแผน",IF(H17-I17&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>รอกำหนด</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="1" t="n">
         <f aca="false">MATCH(E17,บันทึกผล!$G$4:$U$4,0)</f>
         <v>10</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="1" t="n">
         <f aca="false">MATCH(F17,บันทึกผล!$G$4:$U$4,0)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="86.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="str">
+    <row r="18" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A23,FIND(".",บันทึกผล!A23)-1)</f>
         <v>5</v>
       </c>
-      <c r="B18" s="17" t="str">
+      <c r="B18" s="18" t="str">
         <f aca="false">บันทึกผล!A23</f>
         <v>5.1</v>
       </c>
-      <c r="C18" s="18" t="str">
+      <c r="C18" s="19" t="str">
         <f aca="false">บันทึกผล!B23</f>
         <v>ทบทวน/ปรับปรุงนโยบาย กรอบแนวทางการกำกับดูแล และแนวทางการปฏิบัติตามกฎ ระเบียบ ของ กฟน. (Compliance Policy, Framework and Guidance) รวมทั้งแผนการกำกับดูแลฯ เสนอต่อคณะกรรมการที่เกี่ยวข้อง</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">บันทึกผล!D23</f>
         <v>50</v>
       </c>
-      <c r="E18" s="17" t="str">
+      <c r="E18" s="18" t="str">
         <f aca="false">บันทึกผล!E23</f>
         <v>ก.ค.69</v>
       </c>
-      <c r="F18" s="17" t="str">
+      <c r="F18" s="18" t="str">
         <f aca="false">บันทึกผล!F23</f>
         <v>ธ.ค.69</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="20" t="n">
         <f aca="false">N18-M18+1</f>
         <v>6</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H18" s="20" t="n">
         <f aca="false">IF($C$2&lt;M18,0,IF($C$2&gt;=N18,100,ROUND(($C$2-M18+1)/(N18-M18+1)*100,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="I18" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G23:INDEX(บันทึกผล!$G23:$U23,$C$2)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="J18" s="20" t="n">
         <f aca="false">I18-H18</f>
         <v>0</v>
       </c>
-      <c r="K18" s="17" t="str">
+      <c r="K18" s="18" t="str">
         <f aca="false">IF(H18=0,"รอกำหนด",IF(I18&gt;=H18,"ตามแผน",IF(H18-I18&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
-        <v>รอกำหนด</v>
-      </c>
-      <c r="M18" s="0" t="n">
+        <v>ตามแผน</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <f aca="false">MATCH(E18,บันทึกผล!$G$4:$U$4,0)</f>
         <v>7</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="1" t="n">
         <f aca="false">MATCH(F18,บันทึกผล!$G$4:$U$4,0)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="str">
+    <row r="19" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="str">
         <f aca="false">LEFT(บันทึกผล!A24,FIND(".",บันทึกผล!A24)-1)</f>
         <v>5</v>
       </c>
-      <c r="B19" s="17" t="str">
+      <c r="B19" s="18" t="str">
         <f aca="false">บันทึกผล!A24</f>
         <v>5.2</v>
       </c>
-      <c r="C19" s="18" t="str">
+      <c r="C19" s="19" t="str">
         <f aca="false">บันทึกผล!B24</f>
         <v>จัดทำและรายงานการปฏิบัติตามกฎระเบียบ ประจำปี</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <f aca="false">บันทึกผล!D24</f>
         <v>50</v>
       </c>
-      <c r="E19" s="17" t="str">
+      <c r="E19" s="18" t="str">
         <f aca="false">บันทึกผล!E24</f>
         <v>ธ.ค.69</v>
       </c>
-      <c r="F19" s="17" t="str">
+      <c r="F19" s="18" t="str">
         <f aca="false">บันทึกผล!F24</f>
         <v>มี.ค.70</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="20" t="n">
         <f aca="false">N19-M19+1</f>
         <v>4</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="20" t="n">
         <f aca="false">IF($C$2&lt;M19,0,IF($C$2&gt;=N19,100,ROUND(($C$2-M19+1)/(N19-M19+1)*100,0)))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I19" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(9.99E+307,บันทึกผล!$G24:INDEX(บันทึกผล!$G24:$U24,$C$2)),0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="20" t="n">
         <f aca="false">I19-H19</f>
         <v>0</v>
       </c>
-      <c r="K19" s="17" t="str">
+      <c r="K19" s="18" t="str">
         <f aca="false">IF(H19=0,"รอกำหนด",IF(I19&gt;=H19,"ตามแผน",IF(H19-I19&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>รอกำหนด</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19" s="1" t="n">
         <f aca="false">MATCH(E19,บันทึกผล!$G$4:$U$4,0)</f>
         <v>12</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="1" t="n">
         <f aca="false">MATCH(F19,บันทึกผล!$G$4:$U$4,0)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="22" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19),0)</f>
-        <v>49</v>
-      </c>
-      <c r="C23" s="23" t="n">
+        <v>57</v>
+      </c>
+      <c r="C23" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="1")*$D$5:$D$19),0)</f>
-        <v>49</v>
-      </c>
-      <c r="D23" s="23" t="n">
+        <v>57</v>
+      </c>
+      <c r="D23" s="24" t="n">
         <f aca="false">C23-B23</f>
         <v>0</v>
       </c>
-      <c r="E23" s="22" t="str">
+      <c r="E23" s="23" t="str">
         <f aca="false">IF(B23=0,"รอกำหนด",IF(C23&gt;=B23,"ตามแผน",IF(B23-C23&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19),0)</f>
-        <v>67</v>
-      </c>
-      <c r="C24" s="23" t="n">
+        <v>72</v>
+      </c>
+      <c r="C24" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="2")*$D$5:$D$19),0)</f>
-        <v>67</v>
-      </c>
-      <c r="D24" s="23" t="n">
+        <v>72</v>
+      </c>
+      <c r="D24" s="24" t="n">
         <f aca="false">C24-B24</f>
         <v>0</v>
       </c>
-      <c r="E24" s="22" t="str">
+      <c r="E24" s="23" t="str">
         <f aca="false">IF(B24=0,"รอกำหนด",IF(C24&gt;=B24,"ตามแผน",IF(B24-C24&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19),0)</f>
-        <v>46</v>
-      </c>
-      <c r="C25" s="23" t="n">
+        <v>54</v>
+      </c>
+      <c r="C25" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="3")*$D$5:$D$19),0)</f>
-        <v>46</v>
-      </c>
-      <c r="D25" s="23" t="n">
+        <v>54</v>
+      </c>
+      <c r="D25" s="24" t="n">
         <f aca="false">C25-B25</f>
         <v>0</v>
       </c>
-      <c r="E25" s="22" t="str">
+      <c r="E25" s="23" t="str">
         <f aca="false">IF(B25=0,"รอกำหนด",IF(C25&gt;=B25,"ตามแผน",IF(B25-C25&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19),0)</f>
-        <v>15</v>
-      </c>
-      <c r="C26" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="C26" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="4")*$D$5:$D$19),0)</f>
-        <v>15</v>
-      </c>
-      <c r="D26" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="D26" s="24" t="n">
         <f aca="false">C26-B26</f>
         <v>0</v>
       </c>
-      <c r="E26" s="22" t="str">
+      <c r="E26" s="23" t="str">
         <f aca="false">IF(B26=0,"รอกำหนด",IF(C26&gt;=B26,"ตามแผน",IF(B26-C26&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
         <v>ตามแผน</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="23" t="n">
+      <c r="B27" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19*$H$5:$H$19)/SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19),0)</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" s="24" t="n">
         <f aca="false">ROUND(SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19*$I$5:$I$19)/SUMPRODUCT(($A$5:$A$19="5")*$D$5:$D$19),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="24" t="n">
         <f aca="false">C27-B27</f>
         <v>0</v>
       </c>
-      <c r="E27" s="22" t="str">
+      <c r="E27" s="23" t="str">
         <f aca="false">IF(B27=0,"รอกำหนด",IF(C27&gt;=B27,"ตามแผน",IF(B27-C27&lt;=15,"ใกล้เป้า","ต่ำกว่าเป้า")))</f>
-        <v>รอกำหนด</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
+        <v>ตามแผน</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <f aca="false">ROUND(SUMPRODUCT($D$5:$D$19,$H$5:$H$19)/SUM($D$5:$D$19),0)</f>
-        <v>35</v>
-      </c>
-      <c r="C28" s="25" t="n">
+        <v>44</v>
+      </c>
+      <c r="C28" s="26" t="n">
         <f aca="false">ROUND(SUMPRODUCT($D$5:$D$19,$I$5:$I$19)/SUM($D$5:$D$19),0)</f>
-        <v>35</v>
-      </c>
-      <c r="D28" s="25" t="n">
+        <v>44</v>
+      </c>
+      <c r="D28" s="26" t="n">
         <f aca="false">C28-B28</f>
         <v>0</v>
       </c>

--- a/CP_2569_บันทึกผลจริง_template.xlsx
+++ b/CP_2569_บันทึกผลจริง_template.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">สิ่งที่ดำเนินการ มี.ค.70</t>
   </si>
   <si>
-    <t xml:space="preserve">ขั้นที่ 1 · ทบทวนและปรับปรุงทะเบียนกฎหมาย กฎ ระเบียบที่สำคัญที่เกี่ยวข้องกับการดำเนินงาน</t>
+    <t xml:space="preserve">กิจกรรมที่ 1 · ทบทวนและปรับปรุงทะเบียนกฎหมาย กฎ ระเบียบที่สำคัญที่เกี่ยวข้องกับการดำเนินงาน</t>
   </si>
   <si>
     <t xml:space="preserve">1.1</t>
@@ -195,7 +195,7 @@
     <t xml:space="preserve">ฝกม. / ทุกหน่วยงาน</t>
   </si>
   <si>
-    <t xml:space="preserve">ขั้นที่ 2 · ระบุและประเมินปัจจัยความเสี่ยงที่อาจมีผลกระทบต่อองค์กรที่ทำให้ไม่สามารถปฏิบัติตามกฎ ระเบียบ และพิจารณากำหนด/ปรับปรุงการควบคุม</t>
+    <t xml:space="preserve">กิจกรรมที่ 2 · ระบุและประเมินปัจจัยความเสี่ยงที่อาจมีผลกระทบต่อองค์กรที่ทำให้ไม่สามารถปฏิบัติตามกฎ ระเบียบ และพิจารณากำหนด/ปรับปรุงการควบคุม</t>
   </si>
   <si>
     <t xml:space="preserve">2.1</t>
@@ -222,7 +222,7 @@
     <t xml:space="preserve">จัดวาง/ทบทวนระบบการควบคุมภายในของกระบวนงานพื้นฐานและกระบวนงานตามภารกิจของทุกหน่วยงาน</t>
   </si>
   <si>
-    <t xml:space="preserve">ขั้นที่ 3 · สื่อสารความรู้ สร้างความตระหนัก และพัฒนาบุคลากร</t>
+    <t xml:space="preserve">กิจกรรมที่ 3 · สื่อสารความรู้ สร้างความตระหนัก และพัฒนาบุคลากร</t>
   </si>
   <si>
     <t xml:space="preserve">3.1</t>
@@ -249,7 +249,7 @@
     <t xml:space="preserve">ฝบส. / ฝกม.</t>
   </si>
   <si>
-    <t xml:space="preserve">ขั้นที่ 4 · สอบทานและประเมินการปฏิบัติตามกฎ ระเบียบ</t>
+    <t xml:space="preserve">กิจกรรมที่ 4 · สอบทานและประเมินการปฏิบัติตามกฎ ระเบียบ</t>
   </si>
   <si>
     <t xml:space="preserve">4.1</t>
@@ -279,7 +279,7 @@
     <t xml:space="preserve">นำผลประเมินมาปรับปรุงการปฏิบัติงานเพื่อให้เป็นไปตามกฎหมาย กฎ ระเบียบ</t>
   </si>
   <si>
-    <t xml:space="preserve">ขั้นที่ 5 · ทบทวนและนำเสนอผลการทบทวนนโยบาย แนวทางการปฏิบัติ และแผนงานประจำปี ต่อคณะกรรมการที่เกี่ยวข้อง</t>
+    <t xml:space="preserve">กิจกรรมที่ 5 · ทบทวนและนำเสนอผลการทบทวนนโยบาย แนวทางการปฏิบัติ และแผนงานประจำปี ต่อคณะกรรมการที่เกี่ยวข้อง</t>
   </si>
   <si>
     <t xml:space="preserve">5.1</t>
@@ -324,7 +324,7 @@
     <t xml:space="preserve">สรุปรายขั้น (ถ่วงน้ำหนัก)</t>
   </si>
   <si>
-    <t xml:space="preserve">ขั้นที่</t>
+    <t xml:space="preserve">กิจกรรมที่</t>
   </si>
   <si>
     <t xml:space="preserve">รวมทั้งแผน</t>
